--- a/从零开始学Slots/从零开始学Slots-36-番外篇-Python图标结算与添加百搭.xlsx
+++ b/从零开始学Slots/从零开始学Slots-36-番外篇-Python图标结算与添加百搭.xlsx
@@ -4454,6 +4454,9 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <ignoredErrors>
+    <ignoredError sqref="A1:N104" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
@@ -5491,5 +5494,8 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <ignoredErrors>
+    <ignoredError sqref="A1:M84" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
--- a/从零开始学Slots/从零开始学Slots-36-番外篇-Python图标结算与添加百搭.xlsx
+++ b/从零开始学Slots/从零开始学Slots-36-番外篇-Python图标结算与添加百搭.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="148">
   <si>
     <r>
       <rPr>
@@ -3670,7 +3670,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="29">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -3777,6 +3777,14 @@
     </xf>
     <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -4643,14 +4651,14 @@
       <c r="A14" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="B14" s="19" t="s">
-        <v>97</v>
-      </c>
-      <c r="C14" s="19" t="s">
-        <v>98</v>
-      </c>
-      <c r="D14" s="19" t="s">
-        <v>99</v>
+      <c r="B14" s="27">
+        <v>3</v>
+      </c>
+      <c r="C14" s="27">
+        <v>4</v>
+      </c>
+      <c r="D14" s="27">
+        <v>5</v>
       </c>
       <c r="E14" s="13" t="s">
         <v>76</v>
@@ -5387,8 +5395,8 @@
       <c r="E57" s="13"/>
     </row>
     <row r="58" customFormat="false" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="20" t="s">
-        <v>133</v>
+      <c r="A58" s="28">
+        <v>36</v>
       </c>
       <c r="B58" s="20" t="s">
         <v>134</v>
@@ -5400,8 +5408,8 @@
       <c r="E58" s="17"/>
     </row>
     <row r="59" customFormat="false" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="20" t="s">
-        <v>135</v>
+      <c r="A59" s="28">
+        <v>37</v>
       </c>
       <c r="B59" s="20" t="s">
         <v>136</v>
@@ -5413,8 +5421,8 @@
       <c r="E59" s="17"/>
     </row>
     <row r="60" customFormat="false" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="20" t="s">
-        <v>138</v>
+      <c r="A60" s="28">
+        <v>40</v>
       </c>
       <c r="B60" s="20" t="s">
         <v>139</v>
@@ -5426,8 +5434,8 @@
       <c r="E60" s="21"/>
     </row>
     <row r="61" customFormat="false" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="20" t="s">
-        <v>141</v>
+      <c r="A61" s="28">
+        <v>42</v>
       </c>
       <c r="B61" s="17" t="s">
         <v>142</v>
@@ -5439,8 +5447,8 @@
       <c r="E61" s="16"/>
     </row>
     <row r="62" customFormat="false" ht="15.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="20" t="s">
-        <v>144</v>
+      <c r="A62" s="28">
+        <v>38</v>
       </c>
       <c r="B62" s="17" t="s">
         <v>145</v>
